--- a/data.mn/public/datasets/mongolbank-usd-mnt-monthly.xlsx
+++ b/data.mn/public/datasets/mongolbank-usd-mnt-monthly.xlsx
@@ -416,6 +416,43 @@
   </sheetPr>
   <dimension ref="A1:AI13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="26" max="26"/>
+    <col width="9" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="9" customWidth="1" min="32" max="32"/>
+    <col width="9" customWidth="1" min="33" max="33"/>
+    <col width="9" customWidth="1" min="34" max="34"/>
+    <col width="9" customWidth="1" min="35" max="35"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -423,182 +460,112 @@
           <t>Month</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="B1" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C1" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D1" t="n">
+        <v>1995</v>
+      </c>
+      <c r="E1" t="n">
+        <v>1996</v>
+      </c>
+      <c r="F1" t="n">
+        <v>1997</v>
+      </c>
+      <c r="G1" t="n">
+        <v>1998</v>
+      </c>
+      <c r="H1" t="n">
+        <v>1999</v>
+      </c>
+      <c r="I1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J1" t="n">
+        <v>2001</v>
+      </c>
+      <c r="K1" t="n">
+        <v>2002</v>
+      </c>
+      <c r="L1" t="n">
+        <v>2003</v>
+      </c>
+      <c r="M1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="N1" t="n">
+        <v>2005</v>
+      </c>
+      <c r="O1" t="n">
+        <v>2006</v>
+      </c>
+      <c r="P1" t="n">
+        <v>2007</v>
+      </c>
+      <c r="Q1" t="n">
+        <v>2008</v>
+      </c>
+      <c r="R1" t="n">
+        <v>2009</v>
+      </c>
+      <c r="S1" t="n">
+        <v>2010</v>
+      </c>
+      <c r="T1" t="n">
+        <v>2011</v>
+      </c>
+      <c r="U1" t="n">
+        <v>2012</v>
+      </c>
+      <c r="V1" t="n">
+        <v>2013</v>
+      </c>
+      <c r="W1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="X1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AE1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AF1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AG1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AH1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AI1" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="n">
         <v>150</v>
@@ -704,10 +671,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="n">
         <v>150</v>
@@ -813,10 +778,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="n">
         <v>150</v>
@@ -917,13 +880,13 @@
       <c r="AH4" t="n">
         <v>3475.38</v>
       </c>
-      <c r="AI4" t="inlineStr"/>
+      <c r="AI4" t="n">
+        <v>3566.62</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="n">
         <v>150</v>
@@ -1024,13 +987,13 @@
       <c r="AH5" t="n">
         <v>3541.6</v>
       </c>
-      <c r="AI5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>3573.52</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="n">
         <v>187.54</v>
@@ -1131,13 +1094,13 @@
       <c r="AH6" t="n">
         <v>3572.77</v>
       </c>
-      <c r="AI6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>3576.06</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="n">
         <v>398.15</v>
@@ -1238,13 +1201,13 @@
       <c r="AH7" t="n">
         <v>3577.67</v>
       </c>
-      <c r="AI7" t="inlineStr"/>
+      <c r="AI7" t="n">
+        <v>3576.65</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" t="n">
         <v>398.15</v>
@@ -1345,13 +1308,13 @@
       <c r="AH8" t="n">
         <v>3584.83</v>
       </c>
-      <c r="AI8" t="inlineStr"/>
+      <c r="AI8" t="n">
+        <v>3586.77</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="A9" t="n">
+        <v>8</v>
       </c>
       <c r="B9" t="n">
         <v>392.61</v>
@@ -1452,13 +1415,13 @@
       <c r="AH9" t="n">
         <v>3592.14</v>
       </c>
-      <c r="AI9" t="inlineStr"/>
+      <c r="AI9" t="n">
+        <v>3594.47</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="n">
         <v>389.46</v>
@@ -1562,10 +1525,8 @@
       <c r="AI10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="n">
         <v>389.35</v>
@@ -1669,10 +1630,8 @@
       <c r="AI11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A12" t="n">
+        <v>11</v>
       </c>
       <c r="B12" t="n">
         <v>392.86</v>
@@ -1776,10 +1735,8 @@
       <c r="AI12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="n">
         <v>395.03</v>
@@ -1895,6 +1852,43 @@
   </sheetPr>
   <dimension ref="A1:AI13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="26" max="26"/>
+    <col width="9" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="9" customWidth="1" min="32" max="32"/>
+    <col width="9" customWidth="1" min="33" max="33"/>
+    <col width="9" customWidth="1" min="34" max="34"/>
+    <col width="9" customWidth="1" min="35" max="35"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1902,182 +1896,112 @@
           <t>Сар</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="B1" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C1" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D1" t="n">
+        <v>1995</v>
+      </c>
+      <c r="E1" t="n">
+        <v>1996</v>
+      </c>
+      <c r="F1" t="n">
+        <v>1997</v>
+      </c>
+      <c r="G1" t="n">
+        <v>1998</v>
+      </c>
+      <c r="H1" t="n">
+        <v>1999</v>
+      </c>
+      <c r="I1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J1" t="n">
+        <v>2001</v>
+      </c>
+      <c r="K1" t="n">
+        <v>2002</v>
+      </c>
+      <c r="L1" t="n">
+        <v>2003</v>
+      </c>
+      <c r="M1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="N1" t="n">
+        <v>2005</v>
+      </c>
+      <c r="O1" t="n">
+        <v>2006</v>
+      </c>
+      <c r="P1" t="n">
+        <v>2007</v>
+      </c>
+      <c r="Q1" t="n">
+        <v>2008</v>
+      </c>
+      <c r="R1" t="n">
+        <v>2009</v>
+      </c>
+      <c r="S1" t="n">
+        <v>2010</v>
+      </c>
+      <c r="T1" t="n">
+        <v>2011</v>
+      </c>
+      <c r="U1" t="n">
+        <v>2012</v>
+      </c>
+      <c r="V1" t="n">
+        <v>2013</v>
+      </c>
+      <c r="W1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="X1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AE1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AF1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AG1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AH1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AI1" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="n">
         <v>150</v>
@@ -2183,10 +2107,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="n">
         <v>150</v>
@@ -2292,10 +2214,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="n">
         <v>150</v>
@@ -2396,13 +2316,13 @@
       <c r="AH4" t="n">
         <v>3475.38</v>
       </c>
-      <c r="AI4" t="inlineStr"/>
+      <c r="AI4" t="n">
+        <v>3566.62</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="n">
         <v>150</v>
@@ -2503,13 +2423,13 @@
       <c r="AH5" t="n">
         <v>3541.6</v>
       </c>
-      <c r="AI5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>3573.52</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="n">
         <v>187.54</v>
@@ -2610,13 +2530,13 @@
       <c r="AH6" t="n">
         <v>3572.77</v>
       </c>
-      <c r="AI6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>3576.06</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="n">
         <v>398.15</v>
@@ -2717,13 +2637,13 @@
       <c r="AH7" t="n">
         <v>3577.67</v>
       </c>
-      <c r="AI7" t="inlineStr"/>
+      <c r="AI7" t="n">
+        <v>3576.65</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" t="n">
         <v>398.15</v>
@@ -2824,13 +2744,13 @@
       <c r="AH8" t="n">
         <v>3584.83</v>
       </c>
-      <c r="AI8" t="inlineStr"/>
+      <c r="AI8" t="n">
+        <v>3586.77</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="A9" t="n">
+        <v>8</v>
       </c>
       <c r="B9" t="n">
         <v>392.61</v>
@@ -2931,13 +2851,13 @@
       <c r="AH9" t="n">
         <v>3592.14</v>
       </c>
-      <c r="AI9" t="inlineStr"/>
+      <c r="AI9" t="n">
+        <v>3594.47</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="n">
         <v>389.46</v>
@@ -3041,10 +2961,8 @@
       <c r="AI10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="n">
         <v>389.35</v>
@@ -3148,10 +3066,8 @@
       <c r="AI11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A12" t="n">
+        <v>11</v>
       </c>
       <c r="B12" t="n">
         <v>392.86</v>
@@ -3255,10 +3171,8 @@
       <c r="AI12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="n">
         <v>395.03</v>
